--- a/results/tables/tableA5_leave_one_out.xlsx
+++ b/results/tables/tableA5_leave_one_out.xlsx
@@ -61,7 +61,7 @@
     <t>sustained_streak60</t>
   </si>
   <si>
-    <t>crisis_timing_lag0</t>
+    <t>h4_common_exposure_contemp_diff</t>
   </si>
   <si>
     <t>devrel_media_roll24</t>
@@ -82,7 +82,7 @@
     <t>streak_ge60</t>
   </si>
   <si>
-    <t>crisis_media_lag0</t>
+    <t>devrel_media_contemp:is_emergency</t>
   </si>
 </sst>
 </file>
@@ -654,19 +654,19 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>0.0966519096493873</v>
+        <v>0.6738258640553701</v>
       </c>
       <c r="D8">
-        <v>0.008855971894480201</v>
+        <v>1.653402928791792E-06</v>
       </c>
       <c r="E8">
         <v>141</v>
       </c>
       <c r="F8">
-        <v>0.06458305052190599</v>
+        <v>0.5625068082932494</v>
       </c>
       <c r="G8">
-        <v>0.1049391819597195</v>
+        <v>0.7543709485865067</v>
       </c>
       <c r="H8">
         <v>0</v>
